--- a/data/trans_orig/P20-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P20-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2007</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53362</t>
+          <t>52788</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84049</t>
+          <t>84433</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82422</t>
+          <t>82681</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121819</t>
+          <t>120165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144853</t>
+          <t>143288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195241</t>
+          <t>193527</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>947674</t>
+          <t>947290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>978361</t>
+          <t>978935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1193294</t>
+          <t>1194948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1232691</t>
+          <t>1232432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2151594</t>
+          <t>2153308</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2201982</t>
+          <t>2203547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32555</t>
+          <t>33797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60012</t>
+          <t>62547</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95111</t>
+          <t>94558</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138689</t>
+          <t>134492</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136822</t>
+          <t>135391</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>186751</t>
+          <t>186121</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1633401</t>
+          <t>1630866</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1660858</t>
+          <t>1659616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1448984</t>
+          <t>1453181</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1492562</t>
+          <t>1493115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3094335</t>
+          <t>3094965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3144264</t>
+          <t>3145695</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14861</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34507</t>
+          <t>34843</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25145</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47085</t>
+          <t>48576</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44491</t>
+          <t>43842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73870</t>
+          <t>75411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515956</t>
+          <t>515620</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535602</t>
+          <t>535632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>429327</t>
+          <t>427836</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>451267</t>
+          <t>452447</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>953005</t>
+          <t>951464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>982384</t>
+          <t>983033</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114463</t>
+          <t>114249</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>161027</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>221883</t>
+          <t>221283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>285315</t>
+          <t>281499</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>350217</t>
+          <t>347926</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>422044</t>
+          <t>424115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3114572</t>
+          <t>3115209</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3161136</t>
+          <t>3161350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3093882</t>
+          <t>3097698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3157314</t>
+          <t>3157914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6232752</t>
+          <t>6230681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6304579</t>
+          <t>6306870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2012</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81533</t>
+          <t>82942</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121363</t>
+          <t>122288</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114126</t>
+          <t>113653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>159048</t>
+          <t>159473</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203501</t>
+          <t>206367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>265407</t>
+          <t>267648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>853280</t>
+          <t>852355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>893110</t>
+          <t>891701</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1178749</t>
+          <t>1178324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1223671</t>
+          <t>1224144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2047033</t>
+          <t>2044792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2108939</t>
+          <t>2106073</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75541</t>
+          <t>74583</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115445</t>
+          <t>110905</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137442</t>
+          <t>137118</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184785</t>
+          <t>187544</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>223392</t>
+          <t>224459</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>286552</t>
+          <t>287613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1846465</t>
+          <t>1851005</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1886369</t>
+          <t>1887327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1573018</t>
+          <t>1570259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1620361</t>
+          <t>1620685</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3433160</t>
+          <t>3432099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3496320</t>
+          <t>3495253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32350</t>
+          <t>32655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57972</t>
+          <t>57953</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43158</t>
+          <t>43969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73010</t>
+          <t>74832</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>458017</t>
+          <t>455550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>474208</t>
+          <t>473833</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>400659</t>
+          <t>400678</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>426281</t>
+          <t>425976</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>866803</t>
+          <t>864981</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>896655</t>
+          <t>895844</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179262</t>
+          <t>179413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242348</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>304630</t>
+          <t>301982</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>377065</t>
+          <t>375510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>499610</t>
+          <t>503199</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>591127</t>
+          <t>600991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3175386</t>
+          <t>3181648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3238472</t>
+          <t>3238321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3177165</t>
+          <t>3178720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3249600</t>
+          <t>3252248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6380838</t>
+          <t>6370974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6472355</t>
+          <t>6468766</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2016</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42403</t>
+          <t>42070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70576</t>
+          <t>70371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64176</t>
+          <t>64301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103576</t>
+          <t>100311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114223</t>
+          <t>114854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161749</t>
+          <t>161891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>683771</t>
+          <t>683976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>711944</t>
+          <t>712277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>891084</t>
+          <t>894349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>930484</t>
+          <t>930359</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1587258</t>
+          <t>1587116</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1634784</t>
+          <t>1634153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66137</t>
+          <t>65611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101546</t>
+          <t>102998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122201</t>
+          <t>120324</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>169763</t>
+          <t>166487</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198694</t>
+          <t>195720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>258066</t>
+          <t>258278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1974839</t>
+          <t>1973387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2010248</t>
+          <t>2010774</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1818537</t>
+          <t>1821813</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1866099</t>
+          <t>1867976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3806619</t>
+          <t>3806407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3865991</t>
+          <t>3868965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40243</t>
+          <t>38976</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62697</t>
+          <t>60442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57887</t>
+          <t>56940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91514</t>
+          <t>92411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506643</t>
+          <t>507910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530373</t>
+          <t>530934</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>486443</t>
+          <t>488698</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514016</t>
+          <t>513666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1004513</t>
+          <t>1003616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1038140</t>
+          <t>1039087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140185</t>
+          <t>138698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193800</t>
+          <t>193764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>242627</t>
+          <t>243585</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>307018</t>
+          <t>306559</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>395920</t>
+          <t>396379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>482044</t>
+          <t>479854</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3183818</t>
+          <t>3183854</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3237433</t>
+          <t>3238920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3225082</t>
+          <t>3225541</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3289473</t>
+          <t>3288515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6427674</t>
+          <t>6429864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6513798</t>
+          <t>6513339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2023</t>
+          <t>Población que ha estado ingresada en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44380</t>
+          <t>42697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67905</t>
+          <t>68179</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46882</t>
+          <t>46395</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67602</t>
+          <t>67322</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94535</t>
+          <t>96331</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126715</t>
+          <t>128588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>447033</t>
+          <t>446759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470558</t>
+          <t>472241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>685566</t>
+          <t>685846</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>706286</t>
+          <t>706773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1141392</t>
+          <t>1139519</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1173572</t>
+          <t>1171776</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65249</t>
+          <t>65325</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119330</t>
+          <t>118302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86604</t>
+          <t>85464</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144182</t>
+          <t>144380</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>166997</t>
+          <t>171426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>249218</t>
+          <t>248397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2170997</t>
+          <t>2172025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2225078</t>
+          <t>2225002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2093641</t>
+          <t>2093443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2151219</t>
+          <t>2152359</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4278932</t>
+          <t>4279753</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4361153</t>
+          <t>4356724</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26273</t>
+          <t>26914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52215</t>
+          <t>53104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33503</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>56830</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65049</t>
+          <t>66559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99413</t>
+          <t>100377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>594408</t>
+          <t>593519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>620350</t>
+          <t>619709</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>604463</t>
+          <t>603633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626960</t>
+          <t>627468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1207673</t>
+          <t>1206709</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1242037</t>
+          <t>1240527</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144881</t>
+          <t>143214</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>219301</t>
+          <t>218900</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,82 +6586,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>6,34%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>216677</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>172395</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>247093</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>404033</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>344450</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>451417</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>6,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>216677</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>174680</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>249946</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,93%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>404033</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>343633</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>450233</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,69%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3232588</t>
+          <t>3232989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3307008</t>
+          <t>3308675</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,82 +6699,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>93,66%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5008</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3434778</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3404362</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3479060</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>94,07%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>93,23%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>8145</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6699311</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6651927</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6758894</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>94,31%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>93,65%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5008</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3434778</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3401509</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3476775</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,07%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>93,15%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>95,22%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>8145</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6699311</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6653111</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6759711</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>94,31%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>93,66%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P20-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52788</t>
+          <t>53493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>84433</t>
+          <t>84166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82681</t>
+          <t>82028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120165</t>
+          <t>121992</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143288</t>
+          <t>145535</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193527</t>
+          <t>193679</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>947290</t>
+          <t>947557</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>978935</t>
+          <t>978230</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1194948</t>
+          <t>1193121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1232432</t>
+          <t>1233085</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2153308</t>
+          <t>2153156</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2203547</t>
+          <t>2201300</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33797</t>
+          <t>33659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62547</t>
+          <t>59581</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>94558</t>
+          <t>95645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>134492</t>
+          <t>138588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>135391</t>
+          <t>135627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>186121</t>
+          <t>185518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1630866</t>
+          <t>1633832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1659616</t>
+          <t>1659754</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1453181</t>
+          <t>1449085</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1493115</t>
+          <t>1492028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3094965</t>
+          <t>3095568</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3145695</t>
+          <t>3145459</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>14471</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34843</t>
+          <t>34967</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>24583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48576</t>
+          <t>47081</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43842</t>
+          <t>45029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75411</t>
+          <t>73531</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>515620</t>
+          <t>515496</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535632</t>
+          <t>535992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>427836</t>
+          <t>429331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>452447</t>
+          <t>451829</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>951464</t>
+          <t>953344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>983033</t>
+          <t>981846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114249</t>
+          <t>113852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>161439</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>221283</t>
+          <t>217521</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>281499</t>
+          <t>281291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>347926</t>
+          <t>345434</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>424115</t>
+          <t>423699</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3115209</t>
+          <t>3114160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3161350</t>
+          <t>3161747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3097698</t>
+          <t>3097906</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3157914</t>
+          <t>3161676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6230681</t>
+          <t>6231097</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6306870</t>
+          <t>6309362</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,81%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82942</t>
+          <t>81098</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122288</t>
+          <t>121410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113653</t>
+          <t>114938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>159473</t>
+          <t>158396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206367</t>
+          <t>205834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>267648</t>
+          <t>264935</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>852355</t>
+          <t>853233</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>891701</t>
+          <t>893545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1178324</t>
+          <t>1179401</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1224144</t>
+          <t>1222859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2044792</t>
+          <t>2047505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2106073</t>
+          <t>2106606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,1%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74583</t>
+          <t>75289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>110905</t>
+          <t>114873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137118</t>
+          <t>136328</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187544</t>
+          <t>185887</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>224459</t>
+          <t>226432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>287613</t>
+          <t>288195</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1851005</t>
+          <t>1847037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1887327</t>
+          <t>1886621</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1570259</t>
+          <t>1571916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1620685</t>
+          <t>1621475</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3432099</t>
+          <t>3431517</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3495253</t>
+          <t>3493280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25631</t>
+          <t>23901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32655</t>
+          <t>31503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57953</t>
+          <t>57688</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43969</t>
+          <t>42236</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74832</t>
+          <t>72657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>455550</t>
+          <t>457280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473833</t>
+          <t>474275</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>400678</t>
+          <t>400943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425976</t>
+          <t>427128</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>864981</t>
+          <t>867156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>895844</t>
+          <t>897577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179413</t>
+          <t>180594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>236086</t>
+          <t>238467</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>301982</t>
+          <t>305132</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>375510</t>
+          <t>373849</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>503199</t>
+          <t>500036</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>600991</t>
+          <t>599415</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3181648</t>
+          <t>3179267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3238321</t>
+          <t>3237140</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3178720</t>
+          <t>3180381</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3252248</t>
+          <t>3249098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6370974</t>
+          <t>6372550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6468766</t>
+          <t>6471929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42070</t>
+          <t>42037</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70371</t>
+          <t>71148</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>64301</t>
+          <t>63535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>100311</t>
+          <t>101138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114854</t>
+          <t>117097</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161891</t>
+          <t>163888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>683976</t>
+          <t>683199</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>712277</t>
+          <t>712310</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>894349</t>
+          <t>893522</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>930359</t>
+          <t>931125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1587116</t>
+          <t>1585119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1634153</t>
+          <t>1631910</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65611</t>
+          <t>66053</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102998</t>
+          <t>103168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120324</t>
+          <t>123300</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>166487</t>
+          <t>169427</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195720</t>
+          <t>196704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>258278</t>
+          <t>256306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1973387</t>
+          <t>1973217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2010774</t>
+          <t>2010332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1821813</t>
+          <t>1818873</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1867976</t>
+          <t>1865000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3806407</t>
+          <t>3808379</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3868965</t>
+          <t>3867981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15952</t>
+          <t>15964</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38976</t>
+          <t>38989</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35474</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60442</t>
+          <t>62773</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56940</t>
+          <t>57134</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92411</t>
+          <t>93242</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>507910</t>
+          <t>507897</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530934</t>
+          <t>530922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>488698</t>
+          <t>486367</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>513666</t>
+          <t>513013</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1003616</t>
+          <t>1002785</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1039087</t>
+          <t>1038893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138698</t>
+          <t>139987</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193764</t>
+          <t>190747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>243585</t>
+          <t>240987</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>306559</t>
+          <t>308599</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>396379</t>
+          <t>393810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>479854</t>
+          <t>480091</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3183854</t>
+          <t>3186871</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3238920</t>
+          <t>3237631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3225541</t>
+          <t>3223501</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3288515</t>
+          <t>3291113</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6429864</t>
+          <t>6429627</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6513339</t>
+          <t>6515908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>55601</t>
+          <t>58237</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>46290</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68179</t>
+          <t>72805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>55959</t>
+          <t>60498</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46395</t>
+          <t>50405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67322</t>
+          <t>73175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>111561</t>
+          <t>118735</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96331</t>
+          <t>102932</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>128588</t>
+          <t>136292</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>459337</t>
+          <t>520292</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446759</t>
+          <t>505724</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>472241</t>
+          <t>532239</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>697209</t>
+          <t>760817</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>685846</t>
+          <t>748140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>706773</t>
+          <t>770910</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1156546</t>
+          <t>1281110</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1139519</t>
+          <t>1263553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1171776</t>
+          <t>1296913</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>753168</t>
+          <t>821315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1268107</t>
+          <t>1399845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94766</t>
+          <t>105588</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65325</t>
+          <t>85696</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118302</t>
+          <t>127624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>116455</t>
+          <t>134615</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85464</t>
+          <t>113965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144380</t>
+          <t>158435</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>211221</t>
+          <t>240203</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171426</t>
+          <t>212855</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>248397</t>
+          <t>272397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2195561</t>
+          <t>2124978</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2172025</t>
+          <t>2102942</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2225002</t>
+          <t>2144870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2121368</t>
+          <t>2036777</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2093443</t>
+          <t>2012957</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2152359</t>
+          <t>2057427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4316929</t>
+          <t>4161756</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4279753</t>
+          <t>4129562</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4356724</t>
+          <t>4189104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36988</t>
+          <t>40486</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26914</t>
+          <t>28484</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53104</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44263</t>
+          <t>49799</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32995</t>
+          <t>38760</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56830</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>81251</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66559</t>
+          <t>72575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>100377</t>
+          <t>110520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>609635</t>
+          <t>671101</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>593519</t>
+          <t>654206</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>619709</t>
+          <t>683103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>616200</t>
+          <t>685078</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>603633</t>
+          <t>671450</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>627468</t>
+          <t>696117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1225835</t>
+          <t>1356179</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1206709</t>
+          <t>1335944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1240527</t>
+          <t>1373889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,98%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>187356</t>
+          <t>204311</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143214</t>
+          <t>179313</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>218900</t>
+          <t>237195</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>216677</t>
+          <t>244913</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>172395</t>
+          <t>219441</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247093</t>
+          <t>273479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>404033</t>
+          <t>449223</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>344450</t>
+          <t>407373</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>451417</t>
+          <t>492291</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3264533</t>
+          <t>3316372</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3232989</t>
+          <t>3283488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3308675</t>
+          <t>3341370</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3434778</t>
+          <t>3482672</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3404362</t>
+          <t>3454106</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3479060</t>
+          <t>3508144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6699311</t>
+          <t>6799044</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6651927</t>
+          <t>6755976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6758894</t>
+          <t>6840894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3651455</t>
+          <t>3727585</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7103344</t>
+          <t>7248267</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7103344</t>
+          <t>7248267</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7103344</t>
+          <t>7248267</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
